--- a/outputs/q3/solution_audit.xlsx
+++ b/outputs/q3/solution_audit.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58071.56102358679</v>
+        <v>89815.6981543811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9999840333723656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>438270.6025464191</v>
+        <v>416951.2238044906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>713.9252437443503</v>
+        <v>628.5699423658368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.830190986997636</v>
+        <v>0.5538115275841545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
